--- a/Organization_Template_example_data.xlsx
+++ b/Organization_Template_example_data.xlsx
@@ -4506,7 +4506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:I15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" bestFit="1" customWidth="1" style="23" min="1" max="1"/>
@@ -4557,11 +4557,6 @@
       </c>
       <c r="H2" s="32" t="inlineStr">
         <is>
-          <t>DESCRIPTION</t>
-        </is>
-      </c>
-      <c r="I2" s="32" t="inlineStr">
-        <is>
           <t>NOTES</t>
         </is>
       </c>
@@ -4602,12 +4597,7 @@
           <t>s3cur3-pass</t>
         </is>
       </c>
-      <c r="H3" s="25" t="inlineStr">
-        <is>
-          <t>Ignored by the schema (no home for it)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Primary interface for order management</t>
         </is>
@@ -4636,7 +4626,6 @@
       </c>
       <c r="F4" s="25" t="n"/>
       <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4733,7 +4722,7 @@
           <t>ns-pass-2</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>Requires VPN</t>
         </is>
@@ -4814,7 +4803,7 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Legacy EDI connection, rarely used</t>
         </is>
@@ -4856,7 +4845,7 @@
           <t>summit-pass-4</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>OAuth2 credentials rotate every 90 days</t>
         </is>
